--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run2/epoch_70/per_file_predictions_epoch_70.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run2/epoch_70/per_file_predictions_epoch_70.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="492">
   <si>
     <t>Filename</t>
   </si>
@@ -808,700 +808,688 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9333,0.0104,0.0038,0.0145</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.9907,0.0012,0.0006,0.0027</t>
-  </si>
-  <si>
-    <t>0.0116,0.0003,0.0006,0.9949</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9899,0.0022,0.0014,0.0016</t>
+  </si>
+  <si>
+    <t>0.0020,0.0000,0.0000,0.9996</t>
+  </si>
+  <si>
+    <t>0.9909,0.0006,0.0008,0.0047</t>
+  </si>
+  <si>
+    <t>0.0016,0.0027,0.0003,0.9987</t>
+  </si>
+  <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0010,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9917,0.0001,0.0086,0.0000</t>
+  </si>
+  <si>
+    <t>0.0073,0.0002,0.9936,0.0001</t>
+  </si>
+  <si>
+    <t>0.4465,0.0009,0.6710,0.0001</t>
+  </si>
+  <si>
+    <t>0.0021,0.0008,0.9957,0.0005</t>
+  </si>
+  <si>
+    <t>0.9695,0.0004,0.0358,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.9995,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.9979,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.0019,0.9977,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.3669,0.0004,0.6893,0.0006</t>
+  </si>
+  <si>
+    <t>0.9814,0.0001,0.0195,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.9989,0.0002</t>
+  </si>
+  <si>
+    <t>0.0099,0.0010,0.9862,0.0009</t>
+  </si>
+  <si>
+    <t>0.0118,0.0002,0.9898,0.0002</t>
+  </si>
+  <si>
+    <t>0.0028,0.0000,0.9957,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9996,0.0003</t>
+  </si>
+  <si>
+    <t>0.7244,0.4432,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9898,0.0053,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.0007,1.0000,0.0192</t>
+  </si>
+  <si>
+    <t>0.0008,0.9927,0.0236,0.0000</t>
+  </si>
+  <si>
+    <t>0.9962,0.0016,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.2332,0.0039,0.6051,0.0080</t>
+  </si>
+  <si>
+    <t>0.3135,0.6776,0.0102,0.0001</t>
+  </si>
+  <si>
+    <t>0.0023,0.9879,0.1068,0.0001</t>
+  </si>
+  <si>
+    <t>0.0031,0.0035,0.9859,0.0012</t>
+  </si>
+  <si>
+    <t>0.0030,0.0007,0.9947,0.0009</t>
+  </si>
+  <si>
+    <t>0.0124,0.0034,0.9695,0.0017</t>
+  </si>
+  <si>
+    <t>0.0012,0.0000,0.9976,0.0003</t>
+  </si>
+  <si>
+    <t>0.0008,0.0617,0.9940,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.9954,0.0038,0.0001</t>
+  </si>
+  <si>
+    <t>0.0025,0.0003,0.9966,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9874,0.0005,0.1561</t>
+  </si>
+  <si>
+    <t>0.0002,0.9987,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0020,0.9946,0.0035,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0014,0.9992,0.0002</t>
+  </si>
+  <si>
+    <t>0.0028,0.0001,0.9952,0.0005</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0006,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.9943,0.0064,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9941,0.0010,0.0015,0.0008</t>
+  </si>
+  <si>
+    <t>0.9980,0.0013,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9997,0.0047</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9977,0.0012,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9554,0.9165,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0014,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9848,0.9930,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.9986,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9903,0.0002,0.0094,0.0001</t>
+  </si>
+  <si>
+    <t>0.2118,0.0127,0.7211,0.0008</t>
+  </si>
+  <si>
+    <t>0.0002,0.0009,0.9996,0.0017</t>
+  </si>
+  <si>
+    <t>0.0013,0.6126,0.9306,0.0003</t>
+  </si>
+  <si>
+    <t>0.0011,0.7062,0.9043,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.1223,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9902,0.9904,0.0000</t>
+  </si>
+  <si>
+    <t>0.0085,0.0000,0.0006,0.9957</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.0013,0.9993</t>
+  </si>
+  <si>
+    <t>0.0000,0.9976,0.9968,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9726,0.9953,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.3331,0.9832,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.5964,0.9804,0.0005</t>
+  </si>
+  <si>
+    <t>0.0003,0.9454,0.8191,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9969,0.2474,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9981,0.0012,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9951,0.0039,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0013,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9980,0.0006,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9988,0.0011,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0004,0.0011,0.9995,0.0002</t>
+  </si>
+  <si>
+    <t>0.0030,0.0003,0.9972,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0000,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0002,0.9989,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0066,0.9906,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.0028,0.9925,0.0025,0.0008</t>
+  </si>
+  <si>
+    <t>0.0005,0.9993,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.6629,0.3781,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.8687,0.0067,0.0582,0.0010</t>
+  </si>
+  <si>
+    <t>0.2745,0.0000,0.8621,0.0000</t>
+  </si>
+  <si>
+    <t>0.9520,0.0160,0.0069,0.0003</t>
+  </si>
+  <si>
+    <t>0.0970,0.0124,0.7730,0.0149</t>
+  </si>
+  <si>
+    <t>0.0008,0.0005,0.0000,0.9990</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0027,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9975,0.9446,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9992,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.9161,0.0735,0.0056,0.0004</t>
+  </si>
+  <si>
+    <t>0.9707,0.0250,0.0020,0.0001</t>
   </si>
   <si>
     <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9980,0.0002,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9981,0.0005,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.7888,0.9824,0.0003</t>
+  </si>
+  <si>
+    <t>0.0190,0.0458,0.9205,0.0001</t>
+  </si>
+  <si>
+    <t>0.0015,0.0011,0.9973,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0003,0.9985,0.0002</t>
+  </si>
+  <si>
+    <t>0.9250,0.0032,0.0344,0.0015</t>
+  </si>
+  <si>
+    <t>0.9432,0.0000,0.1282,0.0000</t>
+  </si>
+  <si>
+    <t>0.9884,0.0007,0.0042,0.0002</t>
+  </si>
+  <si>
+    <t>0.0116,0.0000,0.0001,0.9970</t>
+  </si>
+  <si>
+    <t>0.0001,0.9838,0.8821,0.0000</t>
+  </si>
+  <si>
+    <t>0.0087,0.9788,0.0052,0.0056</t>
+  </si>
+  <si>
+    <t>0.2837,0.6084,0.0272,0.0003</t>
+  </si>
+  <si>
+    <t>0.9960,0.0003,0.0027,0.0003</t>
+  </si>
+  <si>
+    <t>0.1190,0.0001,0.0003,0.9585</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0142,0.9989,0.0092</t>
+  </si>
+  <si>
+    <t>0.9890,0.0002,0.0041,0.0037</t>
+  </si>
+  <si>
+    <t>0.9810,0.0010,0.0060,0.0022</t>
+  </si>
+  <si>
+    <t>0.0354,0.9510,0.0028,0.0014</t>
+  </si>
+  <si>
+    <t>0.9870,0.0066,0.0015,0.0002</t>
+  </si>
+  <si>
+    <t>0.9879,0.0065,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.9326,0.0470,0.0032,0.0002</t>
+  </si>
+  <si>
+    <t>0.9720,0.0254,0.0016,0.0002</t>
+  </si>
+  <si>
+    <t>0.9981,0.0004,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0005,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9973,0.0008,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9967,0.0014,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.4546,0.2598,0.0002,0.0051</t>
+  </si>
+  <si>
+    <t>0.0510,0.9560,0.0031,0.0000</t>
+  </si>
+  <si>
+    <t>0.4981,0.6368,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.5278,0.0070,0.4181,0.0012</t>
+  </si>
+  <si>
+    <t>0.9862,0.0112,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.7079,0.3389,0.0022,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.0053,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9916,0.0023,0.0025,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0021,0.0077,0.9964,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0000,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0121,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0023,0.9996,0.0003</t>
+  </si>
+  <si>
+    <t>0.0169,0.0015,0.9793,0.0003</t>
+  </si>
+  <si>
+    <t>0.0255,0.0502,0.9310,0.0013</t>
+  </si>
+  <si>
+    <t>0.2471,0.3025,0.1288,0.0015</t>
+  </si>
+  <si>
+    <t>0.1177,0.1909,0.3717,0.0004</t>
+  </si>
+  <si>
+    <t>0.0033,0.0372,0.9760,0.0004</t>
+  </si>
+  <si>
+    <t>0.2615,0.0037,0.8240,0.0002</t>
+  </si>
+  <si>
+    <t>0.5244,0.0037,0.3819,0.0023</t>
+  </si>
+  <si>
+    <t>0.2892,0.0018,0.7206,0.0009</t>
+  </si>
+  <si>
+    <t>0.0119,0.9864,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.0041,0.9959,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.7956,0.2794,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.9101,0.1495,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.2891,0.7980,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9751,0.0031,0.0083,0.0002</t>
+  </si>
+  <si>
+    <t>0.9943,0.0000,0.0057,0.0000</t>
+  </si>
+  <si>
+    <t>0.9440,0.0045,0.0221,0.0032</t>
+  </si>
+  <si>
+    <t>0.9750,0.0014,0.0157,0.0001</t>
+  </si>
+  <si>
+    <t>0.3577,0.0002,0.7238,0.0006</t>
+  </si>
+  <si>
+    <t>0.0131,0.0009,0.9846,0.0018</t>
+  </si>
+  <si>
+    <t>0.0090,0.0074,0.9692,0.0022</t>
+  </si>
+  <si>
+    <t>0.0024,0.0119,0.9956,0.0001</t>
+  </si>
+  <si>
+    <t>0.0031,0.0003,0.9958,0.0001</t>
+  </si>
+  <si>
+    <t>0.0037,0.0063,0.9904,0.0002</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9671,0.0371,0.0008,0.0009</t>
+  </si>
+  <si>
+    <t>0.9989,0.0018,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9979,0.0011,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0004,0.9992,0.0008</t>
+  </si>
+  <si>
+    <t>0.3161,0.3273,0.0786,0.0023</t>
+  </si>
+  <si>
+    <t>0.9482,0.0005,0.0212,0.0099</t>
+  </si>
+  <si>
+    <t>0.0012,0.0001,0.9987,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0497,0.9977,0.0016</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0024,0.0013,0.9949,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0008,0.9984,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.0014,0.9984,0.0002</t>
+  </si>
+  <si>
+    <t>0.9965,0.0001,0.0015,0.0002</t>
+  </si>
+  <si>
+    <t>0.9272,0.0001,0.1450,0.0001</t>
+  </si>
+  <si>
+    <t>0.9955,0.0003,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
     <t>0.9996,0.0003,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9791,0.0006,0.0127,0.0004</t>
-  </si>
-  <si>
-    <t>0.0027,0.0026,0.9939,0.0007</t>
-  </si>
-  <si>
-    <t>0.6488,0.0031,0.3756,0.0001</t>
-  </si>
-  <si>
-    <t>0.0027,0.0003,0.9962,0.0002</t>
-  </si>
-  <si>
-    <t>0.9976,0.0001,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9990,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.0049,0.9935,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.9993,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0093,0.0012,0.9823,0.0016</t>
-  </si>
-  <si>
-    <t>0.9508,0.0002,0.0675,0.0005</t>
-  </si>
-  <si>
-    <t>0.0064,0.0001,0.9949,0.0000</t>
-  </si>
-  <si>
-    <t>0.0056,0.0005,0.9916,0.0003</t>
-  </si>
-  <si>
-    <t>0.2856,0.0000,0.8536,0.0000</t>
-  </si>
-  <si>
-    <t>0.0059,0.0001,0.9928,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9996,0.0002</t>
-  </si>
-  <si>
-    <t>0.1724,0.8907,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.4302,0.3379,0.0153,0.0091</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,1.0000,0.0080</t>
-  </si>
-  <si>
-    <t>0.0006,0.9915,0.0367,0.0001</t>
-  </si>
-  <si>
-    <t>0.9947,0.0046,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.3669,0.0535,0.2292,0.0013</t>
-  </si>
-  <si>
-    <t>0.0848,0.9238,0.0049,0.0001</t>
-  </si>
-  <si>
-    <t>0.0178,0.9538,0.0974,0.0004</t>
-  </si>
-  <si>
-    <t>0.0020,0.0017,0.9914,0.0016</t>
-  </si>
-  <si>
-    <t>0.0162,0.0076,0.9765,0.0065</t>
-  </si>
-  <si>
-    <t>0.0266,0.0021,0.9678,0.0005</t>
-  </si>
-  <si>
-    <t>0.0321,0.0000,0.9781,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0020,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0006,0.9990,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9898,0.0002,0.4594</t>
-  </si>
-  <si>
-    <t>0.0003,0.9993,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9992,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.0714,0.9958,0.0001</t>
-  </si>
-  <si>
-    <t>0.0155,0.0000,0.9861,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.0000,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0010,0.9980,0.0002</t>
-  </si>
-  <si>
-    <t>0.9973,0.0018,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9966,0.0007,0.0010,0.0005</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9999,0.0050</t>
-  </si>
-  <si>
-    <t>0.9982,0.0006,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0005,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9957,0.8305,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0005,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9983,0.9967,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.9928,0.0003,0.0065,0.0001</t>
-  </si>
-  <si>
-    <t>0.2537,0.0126,0.6586,0.0049</t>
-  </si>
-  <si>
-    <t>0.0010,0.0026,0.9984,0.0048</t>
-  </si>
-  <si>
-    <t>0.0000,0.9769,0.9906,0.0000</t>
-  </si>
-  <si>
-    <t>0.0017,0.2006,0.9883,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0017,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9972,0.9785,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0045,0.9993</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0013,0.9998</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0006,0.9995</t>
-  </si>
-  <si>
-    <t>0.0000,0.0005,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9884,0.9840,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9802,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9741,0.9895,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9245,0.8743,0.0012</t>
-  </si>
-  <si>
-    <t>0.0000,0.9990,0.9718,0.0000</t>
-  </si>
-  <si>
-    <t>0.0101,0.6308,0.6382,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0014,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9976,0.0012,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0007,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0005,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0015,0.0009,0.9974,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0015,0.0002,0.9983,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9997,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0062,0.9853,0.0007,0.0034</t>
-  </si>
-  <si>
-    <t>0.0041,0.9917,0.0019,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.9995,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9992,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.5014,0.5507,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.0576,0.3321,0.1341,0.0156</t>
-  </si>
-  <si>
-    <t>0.9673,0.0001,0.0528,0.0001</t>
-  </si>
-  <si>
-    <t>0.9582,0.0052,0.0121,0.0009</t>
-  </si>
-  <si>
-    <t>0.9086,0.0186,0.0290,0.0024</t>
-  </si>
-  <si>
-    <t>0.0005,0.0028,0.0001,0.9987</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9985,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.9967,0.7186,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9994,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9261,0.0561,0.0071,0.0003</t>
-  </si>
-  <si>
-    <t>0.9675,0.0317,0.0017,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9131,0.8631,0.0005</t>
-  </si>
-  <si>
-    <t>0.0111,0.1041,0.9214,0.0000</t>
-  </si>
-  <si>
-    <t>0.0030,0.0004,0.9959,0.0000</t>
-  </si>
-  <si>
-    <t>0.0026,0.0018,0.9941,0.0002</t>
-  </si>
-  <si>
-    <t>0.7815,0.0139,0.0899,0.0042</t>
-  </si>
-  <si>
-    <t>0.0701,0.0000,0.9519,0.0002</t>
-  </si>
-  <si>
-    <t>0.9979,0.0001,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.0001,0.0002,0.9991</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.9956,0.6828,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0084,0.9862,0.0013,0.0016</t>
-  </si>
-  <si>
-    <t>0.1483,0.8163,0.0135,0.0005</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0021,0.0000,0.0021,0.9966</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0064,0.9979,0.0098</t>
-  </si>
-  <si>
-    <t>0.9966,0.0002,0.0015,0.0004</t>
-  </si>
-  <si>
-    <t>0.9222,0.0002,0.0477,0.0028</t>
-  </si>
-  <si>
-    <t>0.0255,0.9022,0.0276,0.0004</t>
-  </si>
-  <si>
-    <t>0.9945,0.0025,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9971,0.0010,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9465,0.0037,0.0266,0.0006</t>
-  </si>
-  <si>
-    <t>0.9111,0.0216,0.0280,0.0004</t>
-  </si>
-  <si>
-    <t>0.9958,0.0017,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9951,0.0012,0.0013,0.0009</t>
-  </si>
-  <si>
-    <t>0.9983,0.0013,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0004,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9987,0.0002,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9944,0.0029,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.8607,0.0899,0.0003,0.0014</t>
-  </si>
-  <si>
-    <t>0.5710,0.4860,0.0046,0.0001</t>
-  </si>
-  <si>
-    <t>0.7802,0.3397,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9660,0.0097,0.0101,0.0012</t>
-  </si>
-  <si>
-    <t>0.9794,0.0181,0.0011,0.0006</t>
-  </si>
-  <si>
-    <t>0.9961,0.0018,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9989,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9936,0.0041,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0009,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0003,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0090,0.0009,0.9901,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0544,0.9983,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.0013,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.2813,0.0014,0.7125,0.0009</t>
-  </si>
-  <si>
-    <t>0.0336,0.0020,0.9610,0.0009</t>
-  </si>
-  <si>
-    <t>0.0062,0.0033,0.9890,0.0002</t>
-  </si>
-  <si>
-    <t>0.1329,0.1411,0.4264,0.0003</t>
-  </si>
-  <si>
-    <t>0.0032,0.4855,0.7978,0.0005</t>
-  </si>
-  <si>
-    <t>0.4203,0.0046,0.5933,0.0005</t>
-  </si>
-  <si>
-    <t>0.0436,0.0059,0.9119,0.0109</t>
-  </si>
-  <si>
-    <t>0.8575,0.0012,0.1605,0.0005</t>
-  </si>
-  <si>
-    <t>0.1181,0.9297,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0081,0.9910,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.9156,0.1066,0.0018,0.0003</t>
-  </si>
-  <si>
-    <t>0.9855,0.0155,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9369,0.0933,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9773,0.0015,0.0125,0.0002</t>
-  </si>
-  <si>
-    <t>0.9968,0.0000,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.9892,0.0004,0.0032,0.0007</t>
-  </si>
-  <si>
-    <t>0.9953,0.0001,0.0021,0.0000</t>
-  </si>
-  <si>
-    <t>0.4266,0.0011,0.6561,0.0009</t>
-  </si>
-  <si>
-    <t>0.0004,0.0002,0.9990,0.0008</t>
-  </si>
-  <si>
-    <t>0.0316,0.0040,0.9543,0.0008</t>
-  </si>
-  <si>
-    <t>0.0033,0.0015,0.9957,0.0000</t>
-  </si>
-  <si>
-    <t>0.1135,0.0000,0.9267,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.0039,0.9965,0.0005</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9974,0.0006,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.9987,0.0008,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0016,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9974,0.0012,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0004,0.9988,0.0009</t>
-  </si>
-  <si>
-    <t>0.0178,0.5394,0.4121,0.0004</t>
-  </si>
-  <si>
-    <t>0.9377,0.0006,0.0024,0.0391</t>
-  </si>
-  <si>
-    <t>0.0023,0.0012,0.9970,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.9999,0.0008</t>
-  </si>
-  <si>
-    <t>0.0009,0.4191,0.9481,0.0011</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0029,0.0011,0.9940,0.0003</t>
-  </si>
-  <si>
-    <t>0.0008,0.0020,0.9971,0.0008</t>
-  </si>
-  <si>
-    <t>0.0170,0.0047,0.9635,0.0024</t>
-  </si>
-  <si>
-    <t>0.9924,0.0001,0.0065,0.0001</t>
-  </si>
-  <si>
-    <t>0.9953,0.0000,0.0048,0.0000</t>
-  </si>
-  <si>
-    <t>0.9979,0.0001,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0008,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9931,0.0064,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9968,0.0027,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9971,0.0036,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0040,0.0203,0.9842,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.0006,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0021,0.0034,0.9945,0.0003</t>
-  </si>
-  <si>
-    <t>0.0066,0.0123,0.9709,0.0015</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.1212,0.0003,0.8830,0.0012</t>
-  </si>
-  <si>
-    <t>0.0013,0.0001,0.9980,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0002,0.9962,0.0024</t>
-  </si>
-  <si>
-    <t>0.9791,0.0000,0.0015,0.0155</t>
-  </si>
-  <si>
-    <t>0.0047,0.0004,0.0000,0.9987</t>
-  </si>
-  <si>
-    <t>0.0028,0.0000,0.0032,0.9967</t>
-  </si>
-  <si>
-    <t>0.9621,0.0005,0.0006,0.0222</t>
+    <t>0.9953,0.0040,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9954,0.0078,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0007,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.1228,0.9951,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.0027,0.9952,0.0015</t>
+  </si>
+  <si>
+    <t>0.0383,0.0314,0.8912,0.0024</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0572,0.0000,0.9417,0.0005</t>
+  </si>
+  <si>
+    <t>0.0018,0.0001,0.9972,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9995,0.0006</t>
+  </si>
+  <si>
+    <t>0.9985,0.0000,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.0201,0.0021,0.0001,0.9932</t>
+  </si>
+  <si>
+    <t>0.0101,0.0000,0.0019,0.9916</t>
+  </si>
+  <si>
+    <t>0.9899,0.0002,0.0002,0.0057</t>
   </si>
 </sst>
 </file>
@@ -1887,7 +1875,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1901,7 +1889,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1915,7 +1903,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1929,7 +1917,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1943,7 +1931,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1957,7 +1945,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1971,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1985,7 +1973,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1999,7 +1987,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2027,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2041,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2055,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2069,7 +2057,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2080,10 +2068,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2097,7 +2085,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2111,7 +2099,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2125,7 +2113,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2139,7 +2127,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2153,7 +2141,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2167,7 +2155,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2181,7 +2169,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2195,7 +2183,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2209,7 +2197,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2223,7 +2211,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2237,7 +2225,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2251,7 +2239,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2265,7 +2253,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2279,7 +2267,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2290,10 +2278,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2307,7 +2295,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2321,7 +2309,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2335,7 +2323,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2349,7 +2337,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2360,10 +2348,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2377,7 +2365,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2391,7 +2379,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2405,7 +2393,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2419,7 +2407,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2433,7 +2421,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2447,7 +2435,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2461,7 +2449,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2475,7 +2463,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2489,7 +2477,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2503,7 +2491,7 @@
         <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2517,7 +2505,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2531,7 +2519,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2545,7 +2533,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2559,7 +2547,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2573,7 +2561,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2587,7 +2575,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2601,7 +2589,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2615,7 +2603,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2629,7 +2617,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2643,7 +2631,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2657,7 +2645,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2671,7 +2659,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2685,7 +2673,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2699,7 +2687,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2713,7 +2701,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2727,7 +2715,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2741,7 +2729,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2755,7 +2743,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2769,7 +2757,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2783,7 +2771,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2797,7 +2785,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2811,7 +2799,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2825,7 +2813,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>284</v>
+        <v>329</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2892,7 +2880,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>334</v>
@@ -3007,7 +2995,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3021,7 +3009,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3035,7 +3023,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3046,10 +3034,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3063,7 +3051,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3077,7 +3065,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3088,10 +3076,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3105,7 +3093,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>268</v>
+        <v>348</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3175,7 +3163,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>353</v>
+        <v>269</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3189,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3203,7 +3191,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>355</v>
+        <v>273</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3217,7 +3205,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3231,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3245,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3259,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3273,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3287,7 +3275,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>268</v>
+        <v>355</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3301,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3315,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3329,7 +3317,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3343,7 +3331,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3357,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3371,7 +3359,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3385,7 +3373,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3399,7 +3387,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3413,7 +3401,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3427,7 +3415,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3441,7 +3429,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3455,7 +3443,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3466,10 +3454,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3483,7 +3471,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3494,10 +3482,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3511,7 +3499,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3522,10 +3510,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3539,7 +3527,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3553,7 +3541,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>374</v>
+        <v>329</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3567,7 +3555,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3581,7 +3569,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3595,7 +3583,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3609,7 +3597,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3623,7 +3611,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3637,7 +3625,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3651,7 +3639,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>274</v>
+        <v>379</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3749,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3763,7 +3751,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3777,7 +3765,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3791,7 +3779,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3805,7 +3793,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3819,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>360</v>
+        <v>270</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3833,7 +3821,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3844,10 +3832,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D142" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3861,7 +3849,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3875,7 +3863,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3903,7 +3891,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3917,7 +3905,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>394</v>
+        <v>338</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3945,7 +3933,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>396</v>
+        <v>270</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3959,7 +3947,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3973,7 +3961,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>383</v>
+        <v>272</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3987,7 +3975,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4001,7 +3989,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4015,7 +4003,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4029,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4043,7 +4031,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4057,7 +4045,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4071,7 +4059,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4085,7 +4073,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4099,7 +4087,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4113,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4127,7 +4115,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4141,7 +4129,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4155,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4169,7 +4157,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4183,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4197,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4211,7 +4199,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4225,7 +4213,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>415</v>
+        <v>380</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4239,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4253,7 +4241,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>351</v>
+        <v>415</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4267,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4278,10 +4266,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D173" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4292,10 +4280,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4306,10 +4294,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4323,7 +4311,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4337,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4351,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4365,7 +4353,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4379,7 +4367,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4393,7 +4381,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4407,7 +4395,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4421,7 +4409,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4435,7 +4423,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4449,7 +4437,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4463,7 +4451,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4477,7 +4465,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4491,7 +4479,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>432</v>
+        <v>327</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4505,7 +4493,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4519,7 +4507,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4533,7 +4521,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4544,10 +4532,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4558,10 +4546,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D193" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4575,7 +4563,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4589,7 +4577,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4600,10 +4588,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4614,10 +4602,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4631,7 +4619,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4645,7 +4633,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4659,7 +4647,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4673,7 +4661,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4684,10 +4672,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4701,7 +4689,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4715,7 +4703,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4729,7 +4717,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4743,7 +4731,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4757,7 +4745,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4771,7 +4759,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4785,7 +4773,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4799,7 +4787,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4813,7 +4801,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4827,7 +4815,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4841,7 +4829,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4855,7 +4843,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4869,7 +4857,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4883,7 +4871,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4897,7 +4885,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4911,7 +4899,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>462</v>
+        <v>421</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4925,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4939,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>396</v>
+        <v>272</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4953,7 +4941,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4964,10 +4952,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D222" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4981,7 +4969,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4995,7 +4983,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5009,7 +4997,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5023,7 +5011,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5037,7 +5025,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5051,7 +5039,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5065,7 +5053,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>315</v>
+        <v>469</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5079,7 +5067,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5093,7 +5081,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5107,7 +5095,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5121,7 +5109,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5135,7 +5123,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5149,7 +5137,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5163,7 +5151,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5177,7 +5165,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>268</v>
+        <v>379</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5191,7 +5179,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5205,7 +5193,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5219,7 +5207,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5233,7 +5221,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5247,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>483</v>
+        <v>460</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5261,7 +5249,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5275,7 +5263,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5289,7 +5277,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5303,7 +5291,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5317,7 +5305,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5331,7 +5319,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5345,7 +5333,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5359,7 +5347,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5373,7 +5361,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5387,7 +5375,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5401,7 +5389,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5443,7 +5431,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
     </row>
   </sheetData>
